--- a/output/review/local-2026-03-21/platelets_review.xlsx
+++ b/output/review/local-2026-03-21/platelets_review.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="platelets" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'platelets'!$A$12:$K$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'platelets'!$A$12:$L$32</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -443,20 +443,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K32"/>
+  <dimension ref="A1:L32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="55" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="55" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
-    <col width="50" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="50" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -592,59 +593,65 @@
       <c r="I12" s="1" t="n"/>
       <c r="J12" s="1" t="n"/>
       <c r="K12" s="1" t="n"/>
+      <c r="L12" s="1" t="n"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>LOINC</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
           <t>SCTID</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>FSN</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>PT</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>Complete aggregation</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>Quantitative (all numeric)</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>Quantitative &amp; convertible</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>Qualitative (ordinal / nominal / presence)</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>Semi-quantitative (test strip)</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>Panel / order code (no Property)</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>Use case</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>Reason</t>
         </is>
@@ -653,27 +660,27 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>104705-9</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>483341010000106</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>Presence of platelet in blood at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Platelets [Presence] in Blood</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
@@ -681,14 +688,14 @@
           <t>·</t>
         </is>
       </c>
-      <c r="G14" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H14" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr">
@@ -696,12 +703,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>qualitative</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>Ordinal/Nominal scale → qualitative</t>
         </is>
@@ -710,27 +722,27 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>9317-9</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>232631010000108</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>Presence of platelet in blood at point in time by light microscopy (observable entity)</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>Platelet adequacy [Presence] in Blood by Light microscopy</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
@@ -738,14 +750,14 @@
           <t>·</t>
         </is>
       </c>
-      <c r="G15" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H15" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
@@ -753,12 +765,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J15" s="2" t="inlineStr">
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>qualitative</t>
         </is>
       </c>
-      <c r="K15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>Ordinal/Nominal scale → qualitative</t>
         </is>
@@ -767,32 +784,32 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>111353-9</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>732051010000102</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>Measurement of platelet in blood (observable entity)</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>Platelets [Measurement] in Blood</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
@@ -810,12 +827,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>quantitative</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>Measurement property, no scale asserted (generic)</t>
         </is>
@@ -824,32 +846,32 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>79427-1</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
           <t>190041010000101</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>Number areic of platelet in blood at point in time by high power field light microscopy (observable entity)</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>Platelets [#/area] in Blood by Microscopy high power field</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
@@ -867,12 +889,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>quantitative</t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale</t>
         </is>
@@ -881,24 +908,24 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>13057-5</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
           <t>156651010000101</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>Arbitrary concentration of platelet in dialysate at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Platelets [Units/volume] in Dialysis fluid</t>
         </is>
       </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -909,9 +936,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G18" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
@@ -924,12 +951,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J18" s="2" t="inlineStr">
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -938,24 +970,24 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>62244-9</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
           <t>66141010000105</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>Number concentration of platelet in Bld^Fetus at point in time by automated count (observable entity)</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>Platelets [#/volume] in Blood from Fetus by Automated count</t>
         </is>
       </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -966,9 +998,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G19" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
@@ -981,12 +1013,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -995,24 +1032,24 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>26515-7</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>90581010000105</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>Number concentration of platelet in blood at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>Platelets [#/volume] in Blood</t>
         </is>
       </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -1023,9 +1060,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G20" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
@@ -1038,12 +1075,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -1052,24 +1094,24 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>777-3</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
           <t>218801010000106</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
         <is>
           <t>Number concentration of platelet in blood at point in time by automated count (observable entity)</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>Platelets [#/volume] in Blood by Automated count</t>
         </is>
       </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -1080,9 +1122,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G21" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
@@ -1095,12 +1137,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J21" s="2" t="inlineStr">
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -1109,24 +1156,24 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>107193-5</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>487891010000102</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
         <is>
           <t>Number concentration of platelet in blood at point in time by automated count in presence of EDTA to detect possible clumping (observable entity)</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>Platelets [#/volume] in Blood by Automated count --in presence of EDTA to detect possible clumping</t>
         </is>
       </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -1137,9 +1184,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G22" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
@@ -1152,12 +1199,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J22" s="2" t="inlineStr">
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -1166,24 +1218,24 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>97995-5</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>56141010000104</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
         <is>
           <t>Number concentration of platelet in blood at point in time by automated count.optical (observable entity)</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Platelets [#/volume] in Blood by Automated count.optical</t>
         </is>
       </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -1194,9 +1246,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G23" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr">
@@ -1209,12 +1261,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -1223,24 +1280,24 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>49497-1</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>86361010000105</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>Number concentration of platelet in blood at point in time by estimate (observable entity)</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Platelets [#/volume] in Blood by Estimate</t>
         </is>
       </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -1251,9 +1308,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G24" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
@@ -1266,12 +1323,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J24" s="2" t="inlineStr">
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -1280,24 +1342,24 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>778-1</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>268771010000105</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t>Number concentration of platelet in blood at point in time by manual count (observable entity)</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>Platelets [#/volume] in Blood by Manual count</t>
         </is>
       </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -1308,9 +1370,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G25" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr">
@@ -1323,12 +1385,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J25" s="2" t="inlineStr">
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K25" s="2" t="inlineStr">
+      <c r="L25" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -1337,24 +1404,24 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>40574-6</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>260911010000103</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>Number concentration of platelet in body fluid at point in time by automated count (observable entity)</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Platelets [#/volume] in Body fluid by Automated count</t>
         </is>
       </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -1365,9 +1432,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G26" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
@@ -1380,12 +1447,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr">
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K26" s="2" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -1394,24 +1466,24 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>74464-9</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
           <t>124101010000103</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
         <is>
           <t>Number concentration of platelet in capillary blood at point in time by manual count (observable entity)</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>Platelets [#/volume] in Capillary blood by Manual count</t>
         </is>
       </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -1422,9 +1494,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G27" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr">
@@ -1437,12 +1509,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J27" s="2" t="inlineStr">
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -1451,24 +1528,24 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>47284-5</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>172051010000108</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t>Number concentration of platelet in cord blood at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Platelets [#/volume] in Cord blood</t>
         </is>
       </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -1479,9 +1556,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G28" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr">
@@ -1494,12 +1571,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J28" s="2" t="inlineStr">
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K28" s="2" t="inlineStr">
+      <c r="L28" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -1508,24 +1590,24 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>55802-3</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
           <t>247121010000104</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
         <is>
           <t>Number concentration of platelet in cord blood at point in time by estimate (observable entity)</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Platelets [#/volume] in Cord blood by Estimate</t>
         </is>
       </c>
-      <c r="D29" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -1536,9 +1618,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G29" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr">
@@ -1551,12 +1633,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J29" s="2" t="inlineStr">
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K29" s="2" t="inlineStr">
+      <c r="L29" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -1565,24 +1652,24 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>26516-5</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
           <t>136661010000100</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
         <is>
           <t>Number concentration of platelet in plasma at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Platelets [#/volume] in Plasma</t>
         </is>
       </c>
-      <c r="D30" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -1593,9 +1680,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G30" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
@@ -1608,12 +1695,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J30" s="2" t="inlineStr">
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K30" s="2" t="inlineStr">
+      <c r="L30" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -1622,24 +1714,24 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>13056-7</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>71831010000107</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
         <is>
           <t>Number concentration of platelet in plasma at point in time by automated count (observable entity)</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>Platelets [#/volume] in Plasma by Automated count</t>
         </is>
       </c>
-      <c r="D31" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -1650,9 +1742,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G31" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr">
@@ -1665,12 +1757,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J31" s="2" t="inlineStr">
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K31" s="2" t="inlineStr">
+      <c r="L31" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -1679,24 +1776,24 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>74775-8</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
           <t>149011010000103</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
         <is>
           <t>Number concentration of platelet in platelet rich plasma at point in time by automated count (observable entity)</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>Platelets [#/volume] in Platelet rich plasma by Automated count</t>
         </is>
       </c>
-      <c r="D32" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -1707,9 +1804,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G32" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
@@ -1722,19 +1819,24 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J32" s="2" t="inlineStr">
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K32" s="2" t="inlineStr">
+      <c r="L32" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A12:K32"/>
+  <autoFilter ref="A12:L32"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>